--- a/Day-04 (18-10-2025)/Day-04(1) (18-10-2025) Table-Pivot Table-CAR-Vendor.xlsx
+++ b/Day-04 (18-10-2025)/Day-04(1) (18-10-2025) Table-Pivot Table-CAR-Vendor.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\IIG\Excel-Tutorial\URI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{268C5424-4603-4A50-ABB3-7E96CC6E96F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86F1FC9E-2BCE-4921-9B83-B2E886626DDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{9E6FED66-A982-4D21-B6E5-3B1C2EA1DA7B}"/>
@@ -30,7 +30,7 @@
   <calcPr calcId="191029"/>
   <pivotCaches>
     <pivotCache cacheId="0" r:id="rId8"/>
-    <pivotCache cacheId="7" r:id="rId9"/>
+    <pivotCache cacheId="2" r:id="rId9"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10468" uniqueCount="2106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10451" uniqueCount="2105">
   <si>
     <t>Make</t>
   </si>
@@ -6355,10 +6355,7 @@
     <t>Sum of Cost</t>
   </si>
   <si>
-    <t>Column Labels</t>
-  </si>
-  <si>
-    <t>Count of Model</t>
+    <t>Sum of Profit</t>
   </si>
 </sst>
 </file>
@@ -6697,314 +6694,25 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="46">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0.00"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0.00"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0.00"/>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left/>
-        <right/>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom/>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </left>
-        <right style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </right>
-        <top style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39997558519241921"/>
-        </bottom>
-      </border>
-    </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0.00"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -7609,6 +7317,295 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="12"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0.00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0.00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0.00"/>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </left>
+        <right style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </right>
+        <top style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.39997558519241921"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
         <color theme="1"/>
         <name val="Calibri"/>
         <family val="2"/>
@@ -7857,6 +7854,1048 @@
 </styleSheet>
 </file>
 
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="104"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="4"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[Day-04(1) (18-10-2025) Table-Pivot Table-CAR-Vendor.xlsx]Sheet3!PivotTable1</c:name>
+    <c:fmtId val="3"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1500" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="100" normalizeH="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent2">
+              <a:lumMod val="20000"/>
+              <a:lumOff val="80000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+          <a:sp3d/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="circle"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln w="22225">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2">
+                <a:alpha val="70000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:view3D>
+      <c:rotX val="15"/>
+      <c:rotY val="20"/>
+      <c:depthPercent val="100"/>
+      <c:rAngAx val="0"/>
+    </c:view3D>
+    <c:floor>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:solidFill>
+          <a:schemeClr val="accent2">
+            <a:alpha val="30000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:floor>
+    <c:sideWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:sideWall>
+    <c:backWall>
+      <c:thickness val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+        <a:sp3d/>
+      </c:spPr>
+    </c:backWall>
+    <c:plotArea>
+      <c:layout/>
+      <c:bar3DChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet3!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2">
+                <a:lumMod val="20000"/>
+                <a:lumOff val="80000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+            <a:sp3d/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet3!$A$4:$A$10</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Chevrolet</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Dodge</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Ford</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Honda</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Nissan</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Toyota</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet3!$B$4:$B$10</c:f>
+              <c:numCache>
+                <c:formatCode>"₹"\ #,##0.00</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>1451</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1391</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2758</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3468</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1710</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1180</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-9122-4F5B-92A4-3C2F9933ACD3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="154"/>
+        <c:gapDepth val="0"/>
+        <c:shape val="box"/>
+        <c:axId val="679635967"/>
+        <c:axId val="679636447"/>
+        <c:axId val="0"/>
+      </c:bar3DChart>
+      <c:catAx>
+        <c:axId val="679635967"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="150" normalizeH="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="679636447"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="679636447"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="&quot;₹&quot;\ #,##0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="679635967"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="accent2"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="accent2"/>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinear" id="15">
+  <a:schemeClr val="accent2"/>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="295">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200" cap="all" spc="150" normalizeH="0" baseline="0"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:alpha val="70000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <cs:styleClr val="auto"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:lumMod val="20000"/>
+          <a:lumOff val="80000"/>
+        </a:schemeClr>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:lumMod val="20000"/>
+          <a:lumOff val="80000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:sp3d/>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="34925" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+      <a:effectLst>
+        <a:outerShdw dist="25400" dir="2700000" algn="tl" rotWithShape="0">
+          <a:schemeClr val="phClr"/>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="22225">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="35000"/>
+          <a:lumOff val="65000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+      <a:effectLst>
+        <a:glow rad="25400">
+          <a:schemeClr val="lt1"/>
+        </a:glow>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr">
+          <a:alpha val="30000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:sp3d/>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="3175" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+            <a:tint val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="1500" b="1" kern="1200" cap="all" spc="100" normalizeH="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:alpha val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="0"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1">
+          <a:lumMod val="95000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>433387</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>147637</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>204787</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>90487</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BCD22EA8-A936-211D-B374-AF0FF0EB1985}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Dell" refreshedDate="45889.713823611113" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="24" xr:uid="{DDE3F5E2-EEF5-4628-9832-E4FCC791F7D4}">
   <cacheSource type="worksheet">
@@ -8044,7 +9083,31 @@
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1500" maxValue="4500"/>
     </cacheField>
     <cacheField name="Profit" numFmtId="164">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="124" maxValue="1000"/>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="124" maxValue="1000" count="23">
+        <n v="1000"/>
+        <n v="500"/>
+        <n v="298"/>
+        <n v="826"/>
+        <n v="470"/>
+        <n v="124"/>
+        <n v="598"/>
+        <n v="160"/>
+        <n v="823"/>
+        <n v="950"/>
+        <n v="459"/>
+        <n v="291"/>
+        <n v="340"/>
+        <n v="361"/>
+        <n v="146"/>
+        <n v="497"/>
+        <n v="606"/>
+        <n v="645"/>
+        <n v="414"/>
+        <n v="559"/>
+        <n v="849"/>
+        <n v="252"/>
+        <n v="290"/>
+      </sharedItems>
     </cacheField>
   </cacheFields>
   <extLst>
@@ -8285,7 +9348,7 @@
     <x v="0"/>
     <n v="4000"/>
     <n v="3000"/>
-    <n v="1000"/>
+    <x v="0"/>
   </r>
   <r>
     <x v="0"/>
@@ -8294,7 +9357,7 @@
     <x v="1"/>
     <n v="2500"/>
     <n v="2000"/>
-    <n v="500"/>
+    <x v="1"/>
   </r>
   <r>
     <x v="0"/>
@@ -8303,7 +9366,7 @@
     <x v="2"/>
     <n v="2000"/>
     <n v="1500"/>
-    <n v="500"/>
+    <x v="1"/>
   </r>
   <r>
     <x v="1"/>
@@ -8312,7 +9375,7 @@
     <x v="3"/>
     <n v="2198"/>
     <n v="1900"/>
-    <n v="298"/>
+    <x v="2"/>
   </r>
   <r>
     <x v="2"/>
@@ -8321,7 +9384,7 @@
     <x v="4"/>
     <n v="3826"/>
     <n v="3000"/>
-    <n v="826"/>
+    <x v="3"/>
   </r>
   <r>
     <x v="2"/>
@@ -8330,7 +9393,7 @@
     <x v="5"/>
     <n v="2970"/>
     <n v="2500"/>
-    <n v="470"/>
+    <x v="4"/>
   </r>
   <r>
     <x v="1"/>
@@ -8339,7 +9402,7 @@
     <x v="6"/>
     <n v="2224"/>
     <n v="2100"/>
-    <n v="124"/>
+    <x v="5"/>
   </r>
   <r>
     <x v="1"/>
@@ -8348,7 +9411,7 @@
     <x v="7"/>
     <n v="2798"/>
     <n v="2200"/>
-    <n v="598"/>
+    <x v="6"/>
   </r>
   <r>
     <x v="1"/>
@@ -8357,7 +9420,7 @@
     <x v="8"/>
     <n v="2160"/>
     <n v="2000"/>
-    <n v="160"/>
+    <x v="7"/>
   </r>
   <r>
     <x v="0"/>
@@ -8366,7 +9429,7 @@
     <x v="9"/>
     <n v="2723"/>
     <n v="1900"/>
-    <n v="823"/>
+    <x v="8"/>
   </r>
   <r>
     <x v="3"/>
@@ -8375,7 +9438,7 @@
     <x v="10"/>
     <n v="3950"/>
     <n v="3000"/>
-    <n v="950"/>
+    <x v="9"/>
   </r>
   <r>
     <x v="4"/>
@@ -8384,7 +9447,7 @@
     <x v="11"/>
     <n v="4959"/>
     <n v="4500"/>
-    <n v="459"/>
+    <x v="10"/>
   </r>
   <r>
     <x v="4"/>
@@ -8393,7 +9456,7 @@
     <x v="12"/>
     <n v="3791"/>
     <n v="3500"/>
-    <n v="291"/>
+    <x v="11"/>
   </r>
   <r>
     <x v="4"/>
@@ -8402,7 +9465,7 @@
     <x v="13"/>
     <n v="2340"/>
     <n v="2000"/>
-    <n v="340"/>
+    <x v="12"/>
   </r>
   <r>
     <x v="4"/>
@@ -8411,7 +9474,7 @@
     <x v="14"/>
     <n v="3361"/>
     <n v="3000"/>
-    <n v="361"/>
+    <x v="13"/>
   </r>
   <r>
     <x v="3"/>
@@ -8420,7 +9483,7 @@
     <x v="15"/>
     <n v="3196"/>
     <n v="3050"/>
-    <n v="146"/>
+    <x v="14"/>
   </r>
   <r>
     <x v="3"/>
@@ -8429,7 +9492,7 @@
     <x v="16"/>
     <n v="4397"/>
     <n v="3900"/>
-    <n v="497"/>
+    <x v="15"/>
   </r>
   <r>
     <x v="3"/>
@@ -8438,7 +9501,7 @@
     <x v="17"/>
     <n v="3706"/>
     <n v="3100"/>
-    <n v="606"/>
+    <x v="16"/>
   </r>
   <r>
     <x v="0"/>
@@ -8447,7 +9510,7 @@
     <x v="18"/>
     <n v="4745"/>
     <n v="4100"/>
-    <n v="645"/>
+    <x v="17"/>
   </r>
   <r>
     <x v="2"/>
@@ -8456,7 +9519,7 @@
     <x v="19"/>
     <n v="2914"/>
     <n v="2500"/>
-    <n v="414"/>
+    <x v="18"/>
   </r>
   <r>
     <x v="3"/>
@@ -8465,7 +9528,7 @@
     <x v="20"/>
     <n v="2659"/>
     <n v="2100"/>
-    <n v="559"/>
+    <x v="19"/>
   </r>
   <r>
     <x v="5"/>
@@ -8474,7 +9537,7 @@
     <x v="21"/>
     <n v="4349"/>
     <n v="3500"/>
-    <n v="849"/>
+    <x v="20"/>
   </r>
   <r>
     <x v="5"/>
@@ -8483,7 +9546,7 @@
     <x v="22"/>
     <n v="4252"/>
     <n v="4000"/>
-    <n v="252"/>
+    <x v="21"/>
   </r>
   <r>
     <x v="5"/>
@@ -8492,7 +9555,7 @@
     <x v="23"/>
     <n v="2090"/>
     <n v="1800"/>
-    <n v="290"/>
+    <x v="22"/>
   </r>
 </pivotCacheRecords>
 </file>
@@ -8583,10 +9646,10 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4B8A53A2-4C19-430B-9305-69052FD9D6D1}" name="PivotTable1" cacheId="7" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
-  <location ref="A3:H20" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4B8A53A2-4C19-430B-9305-69052FD9D6D1}" name="PivotTable1" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
+  <location ref="A3:B10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="7">
-    <pivotField axis="axisCol" showAll="0">
+    <pivotField axis="axisRow" showAll="0">
       <items count="7">
         <item x="4"/>
         <item x="5"/>
@@ -8597,7 +9660,7 @@
         <item t="default"/>
       </items>
     </pivotField>
-    <pivotField axis="axisRow" dataField="1" showAll="0">
+    <pivotField showAll="0">
       <items count="16">
         <item x="0"/>
         <item x="2"/>
@@ -8659,65 +9722,39 @@
     </pivotField>
     <pivotField numFmtId="164" showAll="0"/>
     <pivotField numFmtId="164" showAll="0"/>
-    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField dataField="1" numFmtId="164" showAll="0">
+      <items count="24">
+        <item x="5"/>
+        <item x="14"/>
+        <item x="7"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="11"/>
+        <item x="2"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="18"/>
+        <item x="10"/>
+        <item x="4"/>
+        <item x="15"/>
+        <item x="1"/>
+        <item x="19"/>
+        <item x="6"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="8"/>
+        <item x="3"/>
+        <item x="20"/>
+        <item x="9"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
   </pivotFields>
   <rowFields count="1">
-    <field x="1"/>
+    <field x="0"/>
   </rowFields>
-  <rowItems count="16">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i>
-      <x v="6"/>
-    </i>
-    <i>
-      <x v="7"/>
-    </i>
-    <i>
-      <x v="8"/>
-    </i>
-    <i>
-      <x v="9"/>
-    </i>
-    <i>
-      <x v="10"/>
-    </i>
-    <i>
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="12"/>
-    </i>
-    <i>
-      <x v="13"/>
-    </i>
-    <i>
-      <x v="14"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="0"/>
-  </colFields>
-  <colItems count="7">
+  <rowItems count="7">
     <i>
       <x/>
     </i>
@@ -8739,10 +9776,45 @@
     <i t="grand">
       <x/>
     </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
   </colItems>
   <dataFields count="1">
-    <dataField name="Count of Model" fld="1" subtotal="count" baseField="0" baseItem="0"/>
+    <dataField name="Sum of Profit" fld="6" baseField="0" baseItem="0" numFmtId="164"/>
   </dataFields>
+  <chartFormats count="3">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="0" count="1" selected="0">
+            <x v="3"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -8780,16 +9852,16 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{6C82303B-68FF-44E9-B915-4CDEF03B20F5}" name="Table3" displayName="Table3" ref="A1:G25" totalsRowShown="0" headerRowDxfId="0" tableBorderDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{6C82303B-68FF-44E9-B915-4CDEF03B20F5}" name="Table3" displayName="Table3" ref="A1:G25" totalsRowShown="0" headerRowDxfId="36" tableBorderDxfId="35">
   <autoFilter ref="A1:G25" xr:uid="{6C82303B-68FF-44E9-B915-4CDEF03B20F5}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{D7B027DB-1826-4837-BF4E-2563DC49A64E}" name="Make" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{FBC8BF07-9F6D-4425-93AB-4A33D0602423}" name="Model" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{4F8112E8-FFCD-407B-B7A3-1D2B4664DC19}" name="Colour" dataDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{7D40B81B-041E-4F34-B105-83E0377CD9C7}" name="Mileage" dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{6E98A46F-94EC-43B9-A69D-23EDEB9DE2C6}" name="Price" dataDxfId="3" dataCellStyle="Comma"/>
-    <tableColumn id="6" xr3:uid="{FA4BE187-89D0-4307-9BDF-89309C7F0604}" name="Cost" dataDxfId="2" dataCellStyle="Comma"/>
-    <tableColumn id="7" xr3:uid="{59EA6500-7B1F-42AD-A334-232C66A47796}" name="Profit" dataDxfId="1">
+    <tableColumn id="1" xr3:uid="{D7B027DB-1826-4837-BF4E-2563DC49A64E}" name="Make" dataDxfId="34"/>
+    <tableColumn id="2" xr3:uid="{FBC8BF07-9F6D-4425-93AB-4A33D0602423}" name="Model" dataDxfId="33"/>
+    <tableColumn id="3" xr3:uid="{4F8112E8-FFCD-407B-B7A3-1D2B4664DC19}" name="Colour" dataDxfId="32"/>
+    <tableColumn id="4" xr3:uid="{7D40B81B-041E-4F34-B105-83E0377CD9C7}" name="Mileage" dataDxfId="31"/>
+    <tableColumn id="5" xr3:uid="{6E98A46F-94EC-43B9-A69D-23EDEB9DE2C6}" name="Price" dataDxfId="30" dataCellStyle="Comma"/>
+    <tableColumn id="6" xr3:uid="{FA4BE187-89D0-4307-9BDF-89309C7F0604}" name="Cost" dataDxfId="29" dataCellStyle="Comma"/>
+    <tableColumn id="7" xr3:uid="{59EA6500-7B1F-42AD-A334-232C66A47796}" name="Profit" dataDxfId="28">
       <calculatedColumnFormula>E2-F2</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -8798,42 +9870,42 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FB85749B-95D5-4726-B093-79C085AE386B}" name="Table2" displayName="Table2" ref="A1:N1001" totalsRowShown="0" headerRowDxfId="36" tableBorderDxfId="35">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FB85749B-95D5-4726-B093-79C085AE386B}" name="Table2" displayName="Table2" ref="A1:N1001" totalsRowShown="0" headerRowDxfId="27" tableBorderDxfId="26">
   <autoFilter ref="A1:N1001" xr:uid="{FB85749B-95D5-4726-B093-79C085AE386B}"/>
   <tableColumns count="14">
-    <tableColumn id="1" xr3:uid="{B9FBB25A-3EA1-4CDE-B363-084C178FAE23}" name="EEID" dataDxfId="34"/>
-    <tableColumn id="2" xr3:uid="{26D7861C-7252-48E6-8369-3C436C497501}" name="Full Name" dataDxfId="33"/>
-    <tableColumn id="3" xr3:uid="{8D824609-15AA-432A-B8D4-9E8B82E24C66}" name="Job Title" dataDxfId="32"/>
-    <tableColumn id="4" xr3:uid="{ADCF6FD7-323C-4DB6-9ECD-5AEECEB21D84}" name="Department" dataDxfId="31"/>
-    <tableColumn id="5" xr3:uid="{710CAB83-D3F3-40D1-BF81-10C124A8B248}" name="Business Unit" dataDxfId="30"/>
-    <tableColumn id="6" xr3:uid="{AED2440D-64DA-4B0A-851D-FF741A168ABE}" name="Gender" dataDxfId="29"/>
-    <tableColumn id="7" xr3:uid="{A5D9552A-A462-4103-A8A0-8C0CC550BCFB}" name="Ethnicity" dataDxfId="28"/>
-    <tableColumn id="8" xr3:uid="{D859EB58-E0D0-46E1-9044-7F75DD76B76E}" name="Age" dataDxfId="27"/>
-    <tableColumn id="9" xr3:uid="{1234E203-195F-4578-A3F5-9E3D10702698}" name="Hire Date" dataDxfId="26"/>
-    <tableColumn id="10" xr3:uid="{0F24DD94-670E-4F78-A8D7-0DC78185235D}" name="Annual Salary" dataDxfId="25"/>
-    <tableColumn id="11" xr3:uid="{42BA5936-89AB-4174-92B3-55A8C47D43AE}" name="Bonus %" dataDxfId="24"/>
-    <tableColumn id="12" xr3:uid="{CF74A1A3-3770-4A8D-A680-51786A222F7C}" name="Country" dataDxfId="23"/>
-    <tableColumn id="13" xr3:uid="{41B7E7CE-5484-46B5-8DE6-3EAFA6B5A784}" name="City" dataDxfId="22"/>
-    <tableColumn id="14" xr3:uid="{0F19FF45-69A6-443F-B50D-AE1281873EA2}" name="Exit Date" dataDxfId="21"/>
+    <tableColumn id="1" xr3:uid="{B9FBB25A-3EA1-4CDE-B363-084C178FAE23}" name="EEID" dataDxfId="25"/>
+    <tableColumn id="2" xr3:uid="{26D7861C-7252-48E6-8369-3C436C497501}" name="Full Name" dataDxfId="24"/>
+    <tableColumn id="3" xr3:uid="{8D824609-15AA-432A-B8D4-9E8B82E24C66}" name="Job Title" dataDxfId="23"/>
+    <tableColumn id="4" xr3:uid="{ADCF6FD7-323C-4DB6-9ECD-5AEECEB21D84}" name="Department" dataDxfId="22"/>
+    <tableColumn id="5" xr3:uid="{710CAB83-D3F3-40D1-BF81-10C124A8B248}" name="Business Unit" dataDxfId="21"/>
+    <tableColumn id="6" xr3:uid="{AED2440D-64DA-4B0A-851D-FF741A168ABE}" name="Gender" dataDxfId="20"/>
+    <tableColumn id="7" xr3:uid="{A5D9552A-A462-4103-A8A0-8C0CC550BCFB}" name="Ethnicity" dataDxfId="19"/>
+    <tableColumn id="8" xr3:uid="{D859EB58-E0D0-46E1-9044-7F75DD76B76E}" name="Age" dataDxfId="18"/>
+    <tableColumn id="9" xr3:uid="{1234E203-195F-4578-A3F5-9E3D10702698}" name="Hire Date" dataDxfId="17"/>
+    <tableColumn id="10" xr3:uid="{0F24DD94-670E-4F78-A8D7-0DC78185235D}" name="Annual Salary" dataDxfId="16"/>
+    <tableColumn id="11" xr3:uid="{42BA5936-89AB-4174-92B3-55A8C47D43AE}" name="Bonus %" dataDxfId="15"/>
+    <tableColumn id="12" xr3:uid="{CF74A1A3-3770-4A8D-A680-51786A222F7C}" name="Country" dataDxfId="14"/>
+    <tableColumn id="13" xr3:uid="{41B7E7CE-5484-46B5-8DE6-3EAFA6B5A784}" name="City" dataDxfId="13"/>
+    <tableColumn id="14" xr3:uid="{0F19FF45-69A6-443F-B50D-AE1281873EA2}" name="Exit Date" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{B1AA18D3-771B-4E33-8476-2DD92739C09A}" name="Table5" displayName="Table5" ref="A1:J14" totalsRowShown="0" headerRowDxfId="20" tableBorderDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{B1AA18D3-771B-4E33-8476-2DD92739C09A}" name="Table5" displayName="Table5" ref="A1:J14" totalsRowShown="0" headerRowDxfId="11" tableBorderDxfId="10">
   <autoFilter ref="A1:J14" xr:uid="{B1AA18D3-771B-4E33-8476-2DD92739C09A}"/>
   <tableColumns count="10">
-    <tableColumn id="1" xr3:uid="{C4640AB3-915F-4C4F-BE54-C13E2FB01827}" name="Emp ID" dataDxfId="18"/>
-    <tableColumn id="2" xr3:uid="{1A6D19A4-5B49-41E8-99FC-B547DF63A591}" name="Last Name" dataDxfId="17"/>
-    <tableColumn id="3" xr3:uid="{236BF910-6E6F-459F-A4B1-782BDEF9FFEA}" name="First Name" dataDxfId="16"/>
-    <tableColumn id="4" xr3:uid="{0F05AF2B-946F-40FC-B13F-8D4594F62D5E}" name="Dept" dataDxfId="15"/>
-    <tableColumn id="5" xr3:uid="{B10F05F8-A90B-4BFD-94F9-1885EF4678BD}" name="Full Name" dataDxfId="14"/>
-    <tableColumn id="6" xr3:uid="{D8C16393-38A9-461A-9C59-0F034EECFC81}" name="E-mail" dataDxfId="13"/>
-    <tableColumn id="7" xr3:uid="{1BB8B27E-1457-4DBD-BD6D-C5C43F08DFE9}" name="Phone Ext" dataDxfId="12"/>
-    <tableColumn id="8" xr3:uid="{CEF883F6-989B-436A-83A2-2DDF11DC617E}" name="Location" dataDxfId="11"/>
-    <tableColumn id="9" xr3:uid="{CED62B02-11FC-4901-809B-690352C5731B}" name="Hire Date" dataDxfId="10"/>
-    <tableColumn id="10" xr3:uid="{82287A1F-483D-4E99-B6A7-4A71C4932372}" name="Pay Rate" dataDxfId="9"/>
+    <tableColumn id="1" xr3:uid="{C4640AB3-915F-4C4F-BE54-C13E2FB01827}" name="Emp ID" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{1A6D19A4-5B49-41E8-99FC-B547DF63A591}" name="Last Name" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{236BF910-6E6F-459F-A4B1-782BDEF9FFEA}" name="First Name" dataDxfId="7"/>
+    <tableColumn id="4" xr3:uid="{0F05AF2B-946F-40FC-B13F-8D4594F62D5E}" name="Dept" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{B10F05F8-A90B-4BFD-94F9-1885EF4678BD}" name="Full Name" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{D8C16393-38A9-461A-9C59-0F034EECFC81}" name="E-mail" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{1BB8B27E-1457-4DBD-BD6D-C5C43F08DFE9}" name="Phone Ext" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{CEF883F6-989B-436A-83A2-2DDF11DC617E}" name="Location" dataDxfId="2"/>
+    <tableColumn id="9" xr3:uid="{CED62B02-11FC-4901-809B-690352C5731B}" name="Hire Date" dataDxfId="1"/>
+    <tableColumn id="10" xr3:uid="{82287A1F-483D-4E99-B6A7-4A71C4932372}" name="Pay Rate" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -10422,332 +11494,83 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{489E2E46-6F32-4A90-9C1D-751905DD8D2F}">
-  <dimension ref="A3:H20"/>
+  <dimension ref="A3:B10"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="4.75" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="6.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="5.375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="6.375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11" bestFit="1" customWidth="1"/>
-    <col min="18" max="25" width="6.875" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="23" width="7.875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="53" t="s">
-        <v>2105</v>
-      </c>
-      <c r="B3" s="53" t="s">
+        <v>2101</v>
+      </c>
+      <c r="B3" t="s">
         <v>2104</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" s="53" t="s">
-        <v>2101</v>
-      </c>
-      <c r="B4" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="C4" t="s">
+      <c r="B4" s="58">
+        <v>1451</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="20" t="s">
         <v>32</v>
       </c>
-      <c r="D4" t="s">
+      <c r="B5" s="58">
+        <v>1391</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="E4" t="s">
+      <c r="B6" s="58">
+        <v>2758</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="F4" t="s">
+      <c r="B7" s="58">
+        <v>3468</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="G4" t="s">
+      <c r="B8" s="58">
+        <v>1710</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="H4" t="s">
+      <c r="B9" s="58">
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="20" t="s">
         <v>2102</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="58"/>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58">
-        <v>3</v>
-      </c>
-      <c r="F5" s="58"/>
-      <c r="G5" s="58"/>
-      <c r="H5" s="58">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="20" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="58"/>
-      <c r="C6" s="58"/>
-      <c r="D6" s="58"/>
-      <c r="E6" s="58"/>
-      <c r="F6" s="58">
-        <v>2</v>
-      </c>
-      <c r="G6" s="58"/>
-      <c r="H6" s="58">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="20" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="58"/>
-      <c r="C7" s="58"/>
-      <c r="D7" s="58"/>
-      <c r="E7" s="58"/>
-      <c r="F7" s="58"/>
-      <c r="G7" s="58">
-        <v>1</v>
-      </c>
-      <c r="H7" s="58">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="B8" s="58"/>
-      <c r="C8" s="58">
-        <v>3</v>
-      </c>
-      <c r="D8" s="58"/>
-      <c r="E8" s="58"/>
-      <c r="F8" s="58"/>
-      <c r="G8" s="58"/>
-      <c r="H8" s="58">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="20" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="58"/>
-      <c r="C9" s="58"/>
-      <c r="D9" s="58"/>
-      <c r="E9" s="58">
-        <v>1</v>
-      </c>
-      <c r="F9" s="58"/>
-      <c r="G9" s="58"/>
-      <c r="H9" s="58">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="58"/>
-      <c r="C10" s="58"/>
-      <c r="D10" s="58"/>
-      <c r="E10" s="58"/>
-      <c r="F10" s="58"/>
-      <c r="G10" s="58">
-        <v>3</v>
-      </c>
-      <c r="H10" s="58">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="B11" s="58"/>
-      <c r="C11" s="58"/>
-      <c r="D11" s="58"/>
-      <c r="E11" s="58">
-        <v>1</v>
-      </c>
-      <c r="F11" s="58"/>
-      <c r="G11" s="58"/>
-      <c r="H11" s="58">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="B12" s="58"/>
-      <c r="C12" s="58"/>
-      <c r="D12" s="58">
-        <v>2</v>
-      </c>
-      <c r="E12" s="58"/>
-      <c r="F12" s="58"/>
-      <c r="G12" s="58"/>
-      <c r="H12" s="58">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="20" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" s="58"/>
-      <c r="C13" s="58"/>
-      <c r="D13" s="58">
-        <v>1</v>
-      </c>
-      <c r="E13" s="58"/>
-      <c r="F13" s="58"/>
-      <c r="G13" s="58"/>
-      <c r="H13" s="58">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A14" s="20" t="s">
-        <v>31</v>
-      </c>
-      <c r="B14" s="58"/>
-      <c r="C14" s="58"/>
-      <c r="D14" s="58">
-        <v>1</v>
-      </c>
-      <c r="E14" s="58"/>
-      <c r="F14" s="58"/>
-      <c r="G14" s="58"/>
-      <c r="H14" s="58">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" s="58">
-        <v>2</v>
-      </c>
-      <c r="C15" s="58"/>
-      <c r="D15" s="58"/>
-      <c r="E15" s="58"/>
-      <c r="F15" s="58"/>
-      <c r="G15" s="58"/>
-      <c r="H15" s="58">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A16" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="B16" s="58">
-        <v>1</v>
-      </c>
-      <c r="C16" s="58"/>
-      <c r="D16" s="58"/>
-      <c r="E16" s="58"/>
-      <c r="F16" s="58"/>
-      <c r="G16" s="58"/>
-      <c r="H16" s="58">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="20" t="s">
-        <v>30</v>
-      </c>
-      <c r="B17" s="58"/>
-      <c r="C17" s="58"/>
-      <c r="D17" s="58"/>
-      <c r="E17" s="58"/>
-      <c r="F17" s="58">
-        <v>1</v>
-      </c>
-      <c r="G17" s="58"/>
-      <c r="H17" s="58">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="B18" s="58"/>
-      <c r="C18" s="58"/>
-      <c r="D18" s="58">
-        <v>1</v>
-      </c>
-      <c r="E18" s="58"/>
-      <c r="F18" s="58"/>
-      <c r="G18" s="58"/>
-      <c r="H18" s="58">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="B19" s="58">
-        <v>1</v>
-      </c>
-      <c r="C19" s="58"/>
-      <c r="D19" s="58"/>
-      <c r="E19" s="58"/>
-      <c r="F19" s="58"/>
-      <c r="G19" s="58"/>
-      <c r="H19" s="58">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="20" t="s">
-        <v>2102</v>
-      </c>
-      <c r="B20" s="58">
-        <v>4</v>
-      </c>
-      <c r="C20" s="58">
-        <v>3</v>
-      </c>
-      <c r="D20" s="58">
-        <v>5</v>
-      </c>
-      <c r="E20" s="58">
-        <v>5</v>
-      </c>
-      <c r="F20" s="58">
-        <v>3</v>
-      </c>
-      <c r="G20" s="58">
-        <v>4</v>
-      </c>
-      <c r="H20" s="58">
-        <v>24</v>
+      <c r="B10" s="58">
+        <v>11958</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
